--- a/TEMPLATE FORM A B.xlsx
+++ b/TEMPLATE FORM A B.xlsx
@@ -216,11 +216,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
       <t xml:space="preserve">Jam :  </t>
     </r>
     <r>
@@ -230,7 +225,7 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>07.00</t>
+      <t xml:space="preserve">07.00 </t>
     </r>
     <r>
       <rPr>
@@ -238,41 +233,7 @@
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">   </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">WIB </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">/ WITA / </t>
-    </r>
-    <r>
-      <rPr>
-        <strike/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>WIT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> KET.X=RUSAK</t>
+      <t xml:space="preserve">WITA </t>
     </r>
   </si>
   <si>
@@ -416,15 +377,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="0.0"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* \(#,##0\);_(&quot;Rp&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="0.0"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* \(#,##0\);_(&quot;Rp&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="181" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;?_);_(@_)"/>
     <numFmt numFmtId="182" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="40">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -529,6 +490,51 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -537,22 +543,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -573,21 +566,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -596,9 +574,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -612,9 +589,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -628,31 +604,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -660,13 +628,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -691,12 +652,6 @@
       <name val="Arial"/>
       <charset val="134"/>
     </font>
-    <font>
-      <strike/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -713,37 +668,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,7 +680,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -767,55 +692,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -833,7 +710,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -845,37 +800,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -888,12 +849,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1126,6 +1081,36 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1136,21 +1121,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1170,31 +1140,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1208,164 +1154,173 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="179" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="178" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="26" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="3" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -1418,13 +1373,13 @@
     <xf numFmtId="37" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="9" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="9" xfId="8" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="37" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1445,13 +1400,13 @@
     <xf numFmtId="37" fontId="5" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1463,16 +1418,16 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1486,7 +1441,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1576,7 +1531,7 @@
     <xf numFmtId="182" fontId="5" fillId="0" borderId="16" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1604,13 +1559,16 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="181" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2028,23 +1986,23 @@
       <c r="I1" s="63"/>
       <c r="J1" s="63"/>
       <c r="K1" s="46"/>
-      <c r="L1" s="85" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="85"/>
-      <c r="N1" s="85"/>
-      <c r="O1" s="85"/>
-      <c r="P1" s="85"/>
-      <c r="Q1" s="85"/>
-      <c r="R1" s="85"/>
-      <c r="S1" s="85"/>
-      <c r="T1" s="85"/>
-      <c r="U1" s="85"/>
-      <c r="V1" s="85"/>
-      <c r="W1" s="85"/>
-      <c r="X1" s="85"/>
-      <c r="Y1" s="85"/>
-      <c r="Z1" s="85"/>
+      <c r="L1" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="86"/>
+      <c r="N1" s="86"/>
+      <c r="O1" s="86"/>
+      <c r="P1" s="86"/>
+      <c r="Q1" s="86"/>
+      <c r="R1" s="86"/>
+      <c r="S1" s="86"/>
+      <c r="T1" s="86"/>
+      <c r="U1" s="86"/>
+      <c r="V1" s="86"/>
+      <c r="W1" s="86"/>
+      <c r="X1" s="86"/>
+      <c r="Y1" s="86"/>
+      <c r="Z1" s="86"/>
       <c r="AA1" s="46"/>
       <c r="AB1" s="46"/>
       <c r="AC1" s="46"/>
@@ -2063,7 +2021,7 @@
       </c>
       <c r="B2" s="63"/>
       <c r="C2" s="63"/>
-      <c r="D2" s="96" t="s">
+      <c r="D2" s="97" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="78"/>
@@ -2073,21 +2031,21 @@
       <c r="I2" s="63"/>
       <c r="J2" s="63"/>
       <c r="K2" s="46"/>
-      <c r="L2" s="85"/>
-      <c r="M2" s="85"/>
-      <c r="N2" s="85"/>
-      <c r="O2" s="85"/>
-      <c r="P2" s="85"/>
-      <c r="Q2" s="85"/>
-      <c r="R2" s="85"/>
-      <c r="S2" s="85"/>
-      <c r="T2" s="85"/>
-      <c r="U2" s="85"/>
-      <c r="V2" s="85"/>
-      <c r="W2" s="85"/>
-      <c r="X2" s="85"/>
-      <c r="Y2" s="85"/>
-      <c r="Z2" s="85"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
+      <c r="P2" s="86"/>
+      <c r="Q2" s="86"/>
+      <c r="R2" s="86"/>
+      <c r="S2" s="86"/>
+      <c r="T2" s="86"/>
+      <c r="U2" s="86"/>
+      <c r="V2" s="86"/>
+      <c r="W2" s="86"/>
+      <c r="X2" s="86"/>
+      <c r="Y2" s="86"/>
+      <c r="Z2" s="86"/>
       <c r="AA2" s="46"/>
       <c r="AB2" s="46"/>
       <c r="AC2" s="46"/>
@@ -2097,7 +2055,7 @@
       <c r="AG2" s="46"/>
       <c r="AH2" s="46"/>
       <c r="AI2" s="46"/>
-      <c r="AJ2" s="94" t="s">
+      <c r="AJ2" s="95" t="s">
         <v>3</v>
       </c>
       <c r="AK2" s="62"/>
@@ -2108,7 +2066,7 @@
       </c>
       <c r="B3" s="63"/>
       <c r="C3" s="63"/>
-      <c r="D3" s="96" t="s">
+      <c r="D3" s="97" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="78"/>
@@ -2153,7 +2111,7 @@
       </c>
       <c r="B4" s="63"/>
       <c r="C4" s="63"/>
-      <c r="D4" s="96" t="s">
+      <c r="D4" s="97" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="78"/>
@@ -2164,27 +2122,27 @@
       <c r="J4" s="63"/>
       <c r="K4" s="46"/>
       <c r="L4" s="46"/>
-      <c r="M4" s="86" t="s">
+      <c r="M4" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="N4" s="86"/>
-      <c r="O4" s="86"/>
-      <c r="P4" s="86"/>
-      <c r="Q4" s="86"/>
-      <c r="R4" s="86"/>
-      <c r="S4" s="86"/>
-      <c r="T4" s="86"/>
-      <c r="U4" s="86"/>
-      <c r="V4" s="86"/>
-      <c r="W4" s="86"/>
-      <c r="X4" s="86"/>
-      <c r="Y4" s="86"/>
+      <c r="N4" s="87"/>
+      <c r="O4" s="87"/>
+      <c r="P4" s="87"/>
+      <c r="Q4" s="87"/>
+      <c r="R4" s="87"/>
+      <c r="S4" s="87"/>
+      <c r="T4" s="87"/>
+      <c r="U4" s="87"/>
+      <c r="V4" s="87"/>
+      <c r="W4" s="87"/>
+      <c r="X4" s="87"/>
+      <c r="Y4" s="87"/>
       <c r="Z4" s="46"/>
       <c r="AA4" s="46"/>
       <c r="AB4" s="46"/>
       <c r="AC4" s="46"/>
       <c r="AD4" s="46"/>
-      <c r="AE4" s="93" t="s">
+      <c r="AE4" s="94" t="s">
         <v>10</v>
       </c>
       <c r="AF4" s="46" t="s">
@@ -2202,7 +2160,7 @@
       </c>
       <c r="B5" s="63"/>
       <c r="C5" s="63"/>
-      <c r="D5" s="96" t="s">
+      <c r="D5" s="97" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="78"/>
@@ -2235,7 +2193,7 @@
       <c r="AB5" s="46"/>
       <c r="AC5" s="46"/>
       <c r="AD5" s="46"/>
-      <c r="AE5" s="93" t="s">
+      <c r="AE5" s="94" t="s">
         <v>16</v>
       </c>
       <c r="AF5" s="46" t="s">
@@ -2253,7 +2211,7 @@
       </c>
       <c r="B6" s="63"/>
       <c r="C6" s="63"/>
-      <c r="D6" s="96" t="s">
+      <c r="D6" s="97" t="s">
         <v>19</v>
       </c>
       <c r="E6" s="78"/>
@@ -2272,8 +2230,8 @@
       <c r="R6" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="S6" s="92"/>
-      <c r="T6" s="92"/>
+      <c r="S6" s="93"/>
+      <c r="T6" s="93"/>
       <c r="U6" s="46"/>
       <c r="V6" s="46"/>
       <c r="W6" s="46"/>
@@ -2453,76 +2411,76 @@
         <v>12</v>
       </c>
       <c r="K10" s="52"/>
-      <c r="L10" s="97" t="s">
+      <c r="L10" s="98" t="s">
         <v>27</v>
       </c>
-      <c r="M10" s="97" t="s">
+      <c r="M10" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="N10" s="97" t="s">
+      <c r="N10" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="O10" s="97" t="s">
+      <c r="O10" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="P10" s="97" t="s">
+      <c r="P10" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="Q10" s="97" t="s">
+      <c r="Q10" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="R10" s="97" t="s">
+      <c r="R10" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="S10" s="97" t="s">
+      <c r="S10" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="T10" s="97" t="s">
+      <c r="T10" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="U10" s="97" t="s">
+      <c r="U10" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="V10" s="97" t="s">
+      <c r="V10" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="W10" s="97" t="s">
+      <c r="W10" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="X10" s="97" t="s">
+      <c r="X10" s="98" t="s">
         <v>39</v>
       </c>
-      <c r="Y10" s="97" t="s">
+      <c r="Y10" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="Z10" s="97" t="s">
+      <c r="Z10" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="AA10" s="97" t="s">
+      <c r="AA10" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="AB10" s="97" t="s">
+      <c r="AB10" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="AC10" s="97" t="s">
+      <c r="AC10" s="98" t="s">
         <v>44</v>
       </c>
-      <c r="AD10" s="97" t="s">
+      <c r="AD10" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="AE10" s="97" t="s">
+      <c r="AE10" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="AF10" s="97" t="s">
+      <c r="AF10" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="AG10" s="97" t="s">
+      <c r="AG10" s="98" t="s">
         <v>48</v>
       </c>
-      <c r="AH10" s="97" t="s">
+      <c r="AH10" s="98" t="s">
         <v>49</v>
       </c>
-      <c r="AI10" s="97" t="s">
+      <c r="AI10" s="98" t="s">
         <v>50</v>
       </c>
       <c r="AJ10" s="73"/>
@@ -2618,7 +2576,7 @@
       <c r="J12" s="55">
         <v>0</v>
       </c>
-      <c r="K12" s="87">
+      <c r="K12" s="88">
         <v>1</v>
       </c>
       <c r="L12" s="55">
@@ -2730,7 +2688,7 @@
       <c r="J13" s="55">
         <v>0</v>
       </c>
-      <c r="K13" s="87">
+      <c r="K13" s="88">
         <v>2</v>
       </c>
       <c r="L13" s="55">
@@ -2842,7 +2800,7 @@
       <c r="J14" s="55">
         <v>0</v>
       </c>
-      <c r="K14" s="87">
+      <c r="K14" s="88">
         <v>3</v>
       </c>
       <c r="L14" s="55">
@@ -2954,7 +2912,7 @@
       <c r="J15" s="55">
         <v>0</v>
       </c>
-      <c r="K15" s="87">
+      <c r="K15" s="88">
         <v>4</v>
       </c>
       <c r="L15" s="55">
@@ -3066,7 +3024,7 @@
       <c r="J16" s="55">
         <v>0</v>
       </c>
-      <c r="K16" s="87">
+      <c r="K16" s="88">
         <v>5</v>
       </c>
       <c r="L16" s="55">
@@ -3178,7 +3136,7 @@
       <c r="J17" s="55">
         <v>0</v>
       </c>
-      <c r="K17" s="87">
+      <c r="K17" s="88">
         <v>6</v>
       </c>
       <c r="L17" s="55">
@@ -3290,7 +3248,7 @@
       <c r="J18" s="55">
         <v>0</v>
       </c>
-      <c r="K18" s="87">
+      <c r="K18" s="88">
         <v>7</v>
       </c>
       <c r="L18" s="55">
@@ -3402,7 +3360,7 @@
       <c r="J19" s="55">
         <v>0</v>
       </c>
-      <c r="K19" s="87">
+      <c r="K19" s="88">
         <v>8</v>
       </c>
       <c r="L19" s="55">
@@ -3514,7 +3472,7 @@
       <c r="J20" s="55">
         <v>0</v>
       </c>
-      <c r="K20" s="87">
+      <c r="K20" s="88">
         <v>9</v>
       </c>
       <c r="L20" s="55">
@@ -3626,7 +3584,7 @@
       <c r="J21" s="55">
         <v>0</v>
       </c>
-      <c r="K21" s="87">
+      <c r="K21" s="88">
         <v>10</v>
       </c>
       <c r="L21" s="55">
@@ -3738,7 +3696,7 @@
       <c r="J22" s="55">
         <v>0</v>
       </c>
-      <c r="K22" s="87">
+      <c r="K22" s="88">
         <v>11</v>
       </c>
       <c r="L22" s="55">
@@ -3850,7 +3808,7 @@
       <c r="J23" s="81">
         <v>0</v>
       </c>
-      <c r="K23" s="87">
+      <c r="K23" s="88">
         <v>12</v>
       </c>
       <c r="L23" s="55">
@@ -3962,7 +3920,7 @@
       <c r="J24" s="55">
         <v>0</v>
       </c>
-      <c r="K24" s="87">
+      <c r="K24" s="88">
         <v>13</v>
       </c>
       <c r="L24" s="55">
@@ -4074,7 +4032,7 @@
       <c r="J25" s="55">
         <v>0</v>
       </c>
-      <c r="K25" s="87">
+      <c r="K25" s="88">
         <v>14</v>
       </c>
       <c r="L25" s="55">
@@ -4186,7 +4144,7 @@
       <c r="J26" s="55">
         <v>0</v>
       </c>
-      <c r="K26" s="87">
+      <c r="K26" s="88">
         <v>15</v>
       </c>
       <c r="L26" s="55">
@@ -4298,7 +4256,7 @@
       <c r="J27" s="55">
         <v>0</v>
       </c>
-      <c r="K27" s="87">
+      <c r="K27" s="88">
         <v>16</v>
       </c>
       <c r="L27" s="55">
@@ -4410,7 +4368,7 @@
       <c r="J28" s="82">
         <v>0</v>
       </c>
-      <c r="K28" s="87">
+      <c r="K28" s="88">
         <v>17</v>
       </c>
       <c r="L28" s="55">
@@ -4522,7 +4480,7 @@
       <c r="J29" s="55">
         <v>0</v>
       </c>
-      <c r="K29" s="87">
+      <c r="K29" s="88">
         <v>18</v>
       </c>
       <c r="L29" s="55">
@@ -4597,10 +4555,10 @@
       <c r="AI29" s="55">
         <v>0</v>
       </c>
-      <c r="AJ29" s="95" t="s">
-        <v>53</v>
-      </c>
-      <c r="AK29" s="95"/>
+      <c r="AJ29" s="96" t="s">
+        <v>53</v>
+      </c>
+      <c r="AK29" s="96"/>
     </row>
     <row r="30" ht="13.5" spans="1:37">
       <c r="A30" s="55">
@@ -4633,7 +4591,7 @@
       <c r="J30" s="55">
         <v>0</v>
       </c>
-      <c r="K30" s="87">
+      <c r="K30" s="88">
         <v>19</v>
       </c>
       <c r="L30" s="55">
@@ -4745,7 +4703,7 @@
       <c r="J31" s="55">
         <v>0</v>
       </c>
-      <c r="K31" s="87">
+      <c r="K31" s="88">
         <v>20</v>
       </c>
       <c r="L31" s="55">
@@ -4857,7 +4815,7 @@
       <c r="J32" s="55">
         <v>0</v>
       </c>
-      <c r="K32" s="87">
+      <c r="K32" s="88">
         <v>21</v>
       </c>
       <c r="L32" s="55">
@@ -4969,7 +4927,7 @@
       <c r="J33" s="55">
         <v>0</v>
       </c>
-      <c r="K33" s="87">
+      <c r="K33" s="88">
         <v>22</v>
       </c>
       <c r="L33" s="55">
@@ -5081,7 +5039,7 @@
       <c r="J34" s="55">
         <v>0</v>
       </c>
-      <c r="K34" s="87">
+      <c r="K34" s="88">
         <v>23</v>
       </c>
       <c r="L34" s="55">
@@ -5193,7 +5151,7 @@
       <c r="J35" s="55">
         <v>0</v>
       </c>
-      <c r="K35" s="87">
+      <c r="K35" s="88">
         <v>24</v>
       </c>
       <c r="L35" s="55">
@@ -5305,7 +5263,7 @@
       <c r="J36" s="55">
         <v>0</v>
       </c>
-      <c r="K36" s="87">
+      <c r="K36" s="88">
         <v>25</v>
       </c>
       <c r="L36" s="55">
@@ -5417,7 +5375,7 @@
       <c r="J37" s="55">
         <v>0</v>
       </c>
-      <c r="K37" s="87">
+      <c r="K37" s="88">
         <v>26</v>
       </c>
       <c r="L37" s="55">
@@ -5529,7 +5487,7 @@
       <c r="J38" s="55">
         <v>0</v>
       </c>
-      <c r="K38" s="87">
+      <c r="K38" s="88">
         <v>27</v>
       </c>
       <c r="L38" s="55">
@@ -5641,7 +5599,7 @@
       <c r="J39" s="55">
         <v>0</v>
       </c>
-      <c r="K39" s="87">
+      <c r="K39" s="88">
         <v>28</v>
       </c>
       <c r="L39" s="55">
@@ -5753,7 +5711,7 @@
       <c r="J40" s="55">
         <v>0</v>
       </c>
-      <c r="K40" s="87">
+      <c r="K40" s="88">
         <v>29</v>
       </c>
       <c r="L40" s="55">
@@ -5865,7 +5823,7 @@
       <c r="J41" s="55">
         <v>0</v>
       </c>
-      <c r="K41" s="87">
+      <c r="K41" s="88">
         <v>30</v>
       </c>
       <c r="L41" s="55">
@@ -5977,7 +5935,7 @@
       <c r="J42" s="55">
         <v>0</v>
       </c>
-      <c r="K42" s="87">
+      <c r="K42" s="88">
         <v>31</v>
       </c>
       <c r="L42" s="55">
@@ -6071,79 +6029,103 @@
       <c r="H43" s="83"/>
       <c r="I43" s="83"/>
       <c r="J43" s="83"/>
-      <c r="K43" s="88" t="s">
+      <c r="K43" s="89" t="s">
         <v>55</v>
       </c>
-      <c r="L43" s="89">
-        <v>0</v>
-      </c>
-      <c r="M43" s="89">
-        <v>0</v>
-      </c>
-      <c r="N43" s="89">
-        <v>0</v>
-      </c>
-      <c r="O43" s="89">
-        <v>0</v>
-      </c>
-      <c r="P43" s="89">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="89">
-        <v>0</v>
-      </c>
-      <c r="R43" s="89">
-        <v>0</v>
-      </c>
-      <c r="S43" s="89">
-        <v>0</v>
-      </c>
-      <c r="T43" s="89">
-        <v>0</v>
-      </c>
-      <c r="U43" s="89">
-        <v>0</v>
-      </c>
-      <c r="V43" s="89">
-        <v>0</v>
-      </c>
-      <c r="W43" s="89">
-        <v>0</v>
-      </c>
-      <c r="X43" s="89">
-        <v>0</v>
-      </c>
-      <c r="Y43" s="89">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="89">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="89">
-        <v>0</v>
-      </c>
-      <c r="AB43" s="89">
-        <v>0</v>
-      </c>
-      <c r="AC43" s="89">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="89">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="89">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="89">
-        <v>0</v>
-      </c>
-      <c r="AG43" s="89">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="89">
-        <v>0</v>
-      </c>
-      <c r="AI43" s="89">
+      <c r="L43" s="90">
+        <f>SUM(L12:L42)</f>
+        <v>0</v>
+      </c>
+      <c r="M43" s="90">
+        <f t="shared" ref="M43:AI43" si="2">SUM(M12:M42)</f>
+        <v>0</v>
+      </c>
+      <c r="N43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="R43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="U43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="V43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="W43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="X43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Y43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Z43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AA43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AB43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AC43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AD43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AE43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AF43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AG43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AH43" s="90">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="AI43" s="90">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AJ43" s="57">
@@ -6163,148 +6145,172 @@
       <c r="H44" s="34"/>
       <c r="I44" s="34"/>
       <c r="J44" s="34"/>
-      <c r="K44" s="88"/>
-      <c r="L44" s="89"/>
-      <c r="M44" s="89"/>
-      <c r="N44" s="89"/>
-      <c r="O44" s="89"/>
-      <c r="P44" s="89"/>
-      <c r="Q44" s="89"/>
-      <c r="R44" s="89"/>
-      <c r="S44" s="89"/>
-      <c r="T44" s="89"/>
-      <c r="U44" s="89"/>
-      <c r="V44" s="89"/>
-      <c r="W44" s="89"/>
-      <c r="X44" s="89"/>
-      <c r="Y44" s="89"/>
-      <c r="Z44" s="89"/>
-      <c r="AA44" s="89"/>
-      <c r="AB44" s="89"/>
-      <c r="AC44" s="89"/>
-      <c r="AD44" s="89"/>
-      <c r="AE44" s="89"/>
-      <c r="AF44" s="89"/>
-      <c r="AG44" s="89"/>
-      <c r="AH44" s="89"/>
-      <c r="AI44" s="89"/>
+      <c r="K44" s="89"/>
+      <c r="L44" s="90"/>
+      <c r="M44" s="90"/>
+      <c r="N44" s="90"/>
+      <c r="O44" s="90"/>
+      <c r="P44" s="90"/>
+      <c r="Q44" s="90"/>
+      <c r="R44" s="90"/>
+      <c r="S44" s="90"/>
+      <c r="T44" s="90"/>
+      <c r="U44" s="90"/>
+      <c r="V44" s="90"/>
+      <c r="W44" s="90"/>
+      <c r="X44" s="90"/>
+      <c r="Y44" s="90"/>
+      <c r="Z44" s="90"/>
+      <c r="AA44" s="90"/>
+      <c r="AB44" s="90"/>
+      <c r="AC44" s="90"/>
+      <c r="AD44" s="90"/>
+      <c r="AE44" s="90"/>
+      <c r="AF44" s="90"/>
+      <c r="AG44" s="90"/>
+      <c r="AH44" s="90"/>
+      <c r="AI44" s="90"/>
       <c r="AJ44" s="57"/>
       <c r="AK44" s="57"/>
     </row>
     <row r="45" ht="23.25" customHeight="1" spans="1:37">
       <c r="A45" s="84">
-        <f t="shared" ref="A45:J45" si="2">MAX(A12:A42)</f>
+        <f t="shared" ref="A45:J45" si="3">MAX(A12:A42)</f>
         <v>0</v>
       </c>
       <c r="B45" s="84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="C45" s="84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="D45" s="84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E45" s="84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F45" s="84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G45" s="84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H45" s="84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I45" s="84">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J45" s="84">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K45" s="88" t="s">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="K45" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="L45" s="90">
-        <v>0</v>
-      </c>
-      <c r="M45" s="90">
-        <v>0</v>
-      </c>
-      <c r="N45" s="90">
-        <v>0</v>
-      </c>
-      <c r="O45" s="90">
-        <v>0</v>
-      </c>
-      <c r="P45" s="90">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="90">
-        <v>0</v>
-      </c>
-      <c r="R45" s="90">
-        <v>0</v>
-      </c>
-      <c r="S45" s="90">
-        <v>0</v>
-      </c>
-      <c r="T45" s="90">
-        <v>0</v>
-      </c>
-      <c r="U45" s="90">
-        <v>0</v>
-      </c>
-      <c r="V45" s="90">
-        <v>0</v>
-      </c>
-      <c r="W45" s="90">
-        <v>0</v>
-      </c>
-      <c r="X45" s="90">
-        <v>0</v>
-      </c>
-      <c r="Y45" s="90">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="90">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="90">
-        <v>0</v>
-      </c>
-      <c r="AB45" s="90">
-        <v>0</v>
-      </c>
-      <c r="AC45" s="90">
-        <v>0</v>
-      </c>
-      <c r="AD45" s="90">
-        <v>0</v>
-      </c>
-      <c r="AE45" s="90">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="90">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="90">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="90">
-        <v>0</v>
-      </c>
-      <c r="AI45" s="90">
+      <c r="L45" s="91">
+        <f>MAX(L12:L42)</f>
+        <v>0</v>
+      </c>
+      <c r="M45" s="91">
+        <f t="shared" ref="M45:AI45" si="4">MAX(M12:M42)</f>
+        <v>0</v>
+      </c>
+      <c r="N45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="P45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="R45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="U45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="V45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="W45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="X45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Z45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AB45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AC45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AD45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AE45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AF45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AG45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AH45" s="91">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AI45" s="91">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AJ45" s="57">
@@ -6327,35 +6333,35 @@
       <c r="I46" s="66"/>
       <c r="J46" s="66"/>
       <c r="K46" s="66"/>
-      <c r="L46" s="91"/>
-      <c r="M46" s="91"/>
-      <c r="N46" s="91"/>
-      <c r="O46" s="91"/>
-      <c r="P46" s="91"/>
-      <c r="Q46" s="91"/>
-      <c r="R46" s="91"/>
-      <c r="S46" s="91"/>
-      <c r="T46" s="91"/>
-      <c r="U46" s="91"/>
-      <c r="V46" s="91"/>
-      <c r="W46" s="91"/>
-      <c r="X46" s="91"/>
-      <c r="Y46" s="91"/>
-      <c r="Z46" s="91"/>
-      <c r="AA46" s="91"/>
-      <c r="AB46" s="91"/>
-      <c r="AC46" s="91"/>
-      <c r="AD46" s="91"/>
-      <c r="AE46" s="91"/>
-      <c r="AF46" s="91"/>
-      <c r="AG46" s="91"/>
-      <c r="AH46" s="91"/>
-      <c r="AI46" s="91"/>
-      <c r="AJ46" s="91"/>
-      <c r="AK46" s="91"/>
+      <c r="L46" s="92"/>
+      <c r="M46" s="92"/>
+      <c r="N46" s="92"/>
+      <c r="O46" s="92"/>
+      <c r="P46" s="92"/>
+      <c r="Q46" s="92"/>
+      <c r="R46" s="92"/>
+      <c r="S46" s="92"/>
+      <c r="T46" s="92"/>
+      <c r="U46" s="92"/>
+      <c r="V46" s="92"/>
+      <c r="W46" s="92"/>
+      <c r="X46" s="92"/>
+      <c r="Y46" s="92"/>
+      <c r="Z46" s="92"/>
+      <c r="AA46" s="92"/>
+      <c r="AB46" s="92"/>
+      <c r="AC46" s="92"/>
+      <c r="AD46" s="92"/>
+      <c r="AE46" s="92"/>
+      <c r="AF46" s="92"/>
+      <c r="AG46" s="92"/>
+      <c r="AH46" s="92"/>
+      <c r="AI46" s="92"/>
+      <c r="AJ46" s="92"/>
+      <c r="AK46" s="92"/>
     </row>
     <row r="47" spans="1:37">
-      <c r="A47" s="66" t="s">
+      <c r="A47" s="85" t="s">
         <v>58</v>
       </c>
       <c r="B47" s="66"/>
@@ -6368,32 +6374,32 @@
       <c r="I47" s="66"/>
       <c r="J47" s="66"/>
       <c r="K47" s="66"/>
-      <c r="L47" s="91"/>
-      <c r="M47" s="91"/>
-      <c r="N47" s="91"/>
-      <c r="O47" s="91"/>
-      <c r="P47" s="91"/>
-      <c r="Q47" s="91"/>
-      <c r="R47" s="91"/>
-      <c r="S47" s="91"/>
-      <c r="T47" s="91"/>
-      <c r="U47" s="91"/>
-      <c r="V47" s="91"/>
-      <c r="W47" s="91"/>
-      <c r="X47" s="91"/>
-      <c r="Y47" s="91"/>
-      <c r="Z47" s="91"/>
-      <c r="AA47" s="91"/>
-      <c r="AB47" s="91"/>
-      <c r="AC47" s="91"/>
-      <c r="AD47" s="91"/>
-      <c r="AE47" s="91"/>
-      <c r="AF47" s="91"/>
-      <c r="AG47" s="91"/>
-      <c r="AH47" s="91"/>
-      <c r="AI47" s="91"/>
-      <c r="AJ47" s="91"/>
-      <c r="AK47" s="91"/>
+      <c r="L47" s="92"/>
+      <c r="M47" s="92"/>
+      <c r="N47" s="92"/>
+      <c r="O47" s="92"/>
+      <c r="P47" s="92"/>
+      <c r="Q47" s="92"/>
+      <c r="R47" s="92"/>
+      <c r="S47" s="92"/>
+      <c r="T47" s="92"/>
+      <c r="U47" s="92"/>
+      <c r="V47" s="92"/>
+      <c r="W47" s="92"/>
+      <c r="X47" s="92"/>
+      <c r="Y47" s="92"/>
+      <c r="Z47" s="92"/>
+      <c r="AA47" s="92"/>
+      <c r="AB47" s="92"/>
+      <c r="AC47" s="92"/>
+      <c r="AD47" s="92"/>
+      <c r="AE47" s="92"/>
+      <c r="AF47" s="92"/>
+      <c r="AG47" s="92"/>
+      <c r="AH47" s="92"/>
+      <c r="AI47" s="92"/>
+      <c r="AJ47" s="92"/>
+      <c r="AK47" s="92"/>
     </row>
     <row r="48" spans="1:37">
       <c r="A48" s="58"/>
@@ -6906,7 +6912,7 @@
       </c>
       <c r="B2" s="48"/>
       <c r="C2" s="48"/>
-      <c r="D2" s="98" t="s">
+      <c r="D2" s="99" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="50"/>
@@ -6941,7 +6947,7 @@
       </c>
       <c r="B3" s="48"/>
       <c r="C3" s="48"/>
-      <c r="D3" s="98" t="s">
+      <c r="D3" s="99" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="50"/>
@@ -6976,7 +6982,7 @@
       </c>
       <c r="B4" s="48"/>
       <c r="C4" s="48"/>
-      <c r="D4" s="98" t="s">
+      <c r="D4" s="99" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="50"/>
@@ -7180,76 +7186,76 @@
     </row>
     <row r="10" ht="13.5" customHeight="1" spans="1:27">
       <c r="A10" s="52"/>
-      <c r="B10" s="97" t="s">
+      <c r="B10" s="98" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="97" t="s">
+      <c r="C10" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="97" t="s">
+      <c r="D10" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="97" t="s">
+      <c r="E10" s="98" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="97" t="s">
+      <c r="F10" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="97" t="s">
+      <c r="G10" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="97" t="s">
+      <c r="H10" s="98" t="s">
         <v>33</v>
       </c>
-      <c r="I10" s="97" t="s">
+      <c r="I10" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="97" t="s">
+      <c r="J10" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="K10" s="97" t="s">
+      <c r="K10" s="98" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="97" t="s">
+      <c r="L10" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="M10" s="97" t="s">
+      <c r="M10" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="N10" s="97" t="s">
+      <c r="N10" s="98" t="s">
         <v>39</v>
       </c>
-      <c r="O10" s="97" t="s">
+      <c r="O10" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="P10" s="97" t="s">
+      <c r="P10" s="98" t="s">
         <v>41</v>
       </c>
-      <c r="Q10" s="97" t="s">
+      <c r="Q10" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="R10" s="97" t="s">
+      <c r="R10" s="98" t="s">
         <v>43</v>
       </c>
-      <c r="S10" s="97" t="s">
+      <c r="S10" s="98" t="s">
         <v>44</v>
       </c>
-      <c r="T10" s="97" t="s">
+      <c r="T10" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="U10" s="97" t="s">
+      <c r="U10" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="V10" s="97" t="s">
+      <c r="V10" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="W10" s="97" t="s">
+      <c r="W10" s="98" t="s">
         <v>48</v>
       </c>
-      <c r="X10" s="97" t="s">
+      <c r="X10" s="98" t="s">
         <v>49</v>
       </c>
-      <c r="Y10" s="97" t="s">
+      <c r="Y10" s="98" t="s">
         <v>50</v>
       </c>
       <c r="Z10" s="73"/>
